--- a/template/report-template.xlsx
+++ b/template/report-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f6b5412d5ab48344/Desktop/完成図書アプリ化/素材/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="14_{31601A9F-1552-4756-84EB-397D4253546A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD3DE30E-FD21-4DE5-B617-33F6B0858075}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="14_{31601A9F-1552-4756-84EB-397D4253546A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E312923C-1410-4137-BB64-1E337CA07016}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="完了報告書" sheetId="1" r:id="rId1"/>
@@ -73,9 +73,6 @@
   </si>
   <si>
     <t>実施担当者</t>
-  </si>
-  <si>
-    <t>【チェック項目】</t>
   </si>
   <si>
     <t>電源数</t>
@@ -174,13 +171,23 @@
     <t>⑧</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>【電源情報】</t>
+    <rPh sb="1" eb="3">
+      <t>デンゲン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="180" formatCode="h:mm;@"/>
+    <numFmt numFmtId="176" formatCode="h:mm;@"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -309,7 +316,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -331,6 +338,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="45"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -692,7 +705,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -781,41 +794,72 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="31" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -836,35 +880,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -879,14 +894,54 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="・_1_8.5.27～8.6.2_1_XX月XX日 木曜日 _12月26日 金曜日 " xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1331,122 +1386,122 @@
       <c r="AZ1" s="23"/>
     </row>
     <row r="2" spans="1:56" ht="13.5" customHeight="1">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="36"/>
-      <c r="Y2" s="36"/>
-      <c r="Z2" s="36"/>
-      <c r="AA2" s="36"/>
-      <c r="AB2" s="36"/>
-      <c r="AC2" s="36"/>
-      <c r="AD2" s="36"/>
-      <c r="AE2" s="36"/>
-      <c r="AF2" s="36"/>
-      <c r="AG2" s="36"/>
-      <c r="AH2" s="36"/>
-      <c r="AI2" s="36"/>
-      <c r="AJ2" s="36"/>
-      <c r="AK2" s="36"/>
-      <c r="AL2" s="36"/>
-      <c r="AM2" s="36"/>
-      <c r="AN2" s="36"/>
-      <c r="AO2" s="36"/>
-      <c r="AP2" s="36"/>
-      <c r="AQ2" s="36"/>
-      <c r="AR2" s="36"/>
-      <c r="AS2" s="36"/>
-      <c r="AT2" s="36"/>
-      <c r="AU2" s="36"/>
-      <c r="AV2" s="36"/>
-      <c r="AW2" s="36"/>
-      <c r="AX2" s="36"/>
-      <c r="AY2" s="36"/>
-      <c r="AZ2" s="36"/>
-      <c r="BA2" s="36"/>
-      <c r="BB2" s="36"/>
-      <c r="BC2" s="36"/>
-      <c r="BD2" s="36"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="43"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="43"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="43"/>
+      <c r="AA2" s="43"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="43"/>
+      <c r="AE2" s="43"/>
+      <c r="AF2" s="43"/>
+      <c r="AG2" s="43"/>
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="43"/>
+      <c r="AJ2" s="43"/>
+      <c r="AK2" s="43"/>
+      <c r="AL2" s="43"/>
+      <c r="AM2" s="43"/>
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="43"/>
+      <c r="AP2" s="43"/>
+      <c r="AQ2" s="43"/>
+      <c r="AR2" s="43"/>
+      <c r="AS2" s="43"/>
+      <c r="AT2" s="43"/>
+      <c r="AU2" s="43"/>
+      <c r="AV2" s="43"/>
+      <c r="AW2" s="43"/>
+      <c r="AX2" s="43"/>
+      <c r="AY2" s="43"/>
+      <c r="AZ2" s="43"/>
+      <c r="BA2" s="43"/>
+      <c r="BB2" s="43"/>
+      <c r="BC2" s="43"/>
+      <c r="BD2" s="43"/>
     </row>
     <row r="3" spans="1:56" ht="13.5" customHeight="1">
-      <c r="A3" s="36"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="36"/>
-      <c r="P3" s="36"/>
-      <c r="Q3" s="36"/>
-      <c r="R3" s="36"/>
-      <c r="S3" s="36"/>
-      <c r="T3" s="36"/>
-      <c r="U3" s="36"/>
-      <c r="V3" s="36"/>
-      <c r="W3" s="36"/>
-      <c r="X3" s="36"/>
-      <c r="Y3" s="36"/>
-      <c r="Z3" s="36"/>
-      <c r="AA3" s="36"/>
-      <c r="AB3" s="36"/>
-      <c r="AC3" s="36"/>
-      <c r="AD3" s="36"/>
-      <c r="AE3" s="36"/>
-      <c r="AF3" s="36"/>
-      <c r="AG3" s="36"/>
-      <c r="AH3" s="36"/>
-      <c r="AI3" s="36"/>
-      <c r="AJ3" s="36"/>
-      <c r="AK3" s="36"/>
-      <c r="AL3" s="36"/>
-      <c r="AM3" s="36"/>
-      <c r="AN3" s="36"/>
-      <c r="AO3" s="36"/>
-      <c r="AP3" s="36"/>
-      <c r="AQ3" s="36"/>
-      <c r="AR3" s="36"/>
-      <c r="AS3" s="36"/>
-      <c r="AT3" s="36"/>
-      <c r="AU3" s="36"/>
-      <c r="AV3" s="36"/>
-      <c r="AW3" s="36"/>
-      <c r="AX3" s="36"/>
-      <c r="AY3" s="36"/>
-      <c r="AZ3" s="36"/>
-      <c r="BA3" s="36"/>
-      <c r="BB3" s="36"/>
-      <c r="BC3" s="36"/>
-      <c r="BD3" s="36"/>
+      <c r="A3" s="43"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="43"/>
+      <c r="Y3" s="43"/>
+      <c r="Z3" s="43"/>
+      <c r="AA3" s="43"/>
+      <c r="AB3" s="43"/>
+      <c r="AC3" s="43"/>
+      <c r="AD3" s="43"/>
+      <c r="AE3" s="43"/>
+      <c r="AF3" s="43"/>
+      <c r="AG3" s="43"/>
+      <c r="AH3" s="43"/>
+      <c r="AI3" s="43"/>
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="43"/>
+      <c r="AP3" s="43"/>
+      <c r="AQ3" s="43"/>
+      <c r="AR3" s="43"/>
+      <c r="AS3" s="43"/>
+      <c r="AT3" s="43"/>
+      <c r="AU3" s="43"/>
+      <c r="AV3" s="43"/>
+      <c r="AW3" s="43"/>
+      <c r="AX3" s="43"/>
+      <c r="AY3" s="43"/>
+      <c r="AZ3" s="43"/>
+      <c r="BA3" s="43"/>
+      <c r="BB3" s="43"/>
+      <c r="BC3" s="43"/>
+      <c r="BD3" s="43"/>
     </row>
     <row r="4" spans="1:56" ht="12.75" customHeight="1">
       <c r="A4" s="10"/>
@@ -1512,228 +1567,228 @@
       </c>
     </row>
     <row r="6" spans="1:56">
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="52"/>
-      <c r="P6" s="52"/>
-      <c r="Q6" s="52"/>
-      <c r="R6" s="52"/>
-      <c r="S6" s="52"/>
-      <c r="T6" s="52"/>
-      <c r="U6" s="52"/>
-      <c r="V6" s="52"/>
-      <c r="W6" s="52"/>
-      <c r="X6" s="52"/>
-      <c r="Y6" s="52"/>
-      <c r="Z6" s="52"/>
-      <c r="AA6" s="52"/>
-      <c r="AB6" s="52"/>
-      <c r="AC6" s="52"/>
-      <c r="AD6" s="52"/>
-      <c r="AE6" s="52"/>
-      <c r="AF6" s="52"/>
-      <c r="AG6" s="53"/>
-      <c r="AH6" s="43" t="s">
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="67"/>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="67"/>
+      <c r="T6" s="67"/>
+      <c r="U6" s="67"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="67"/>
+      <c r="X6" s="67"/>
+      <c r="Y6" s="67"/>
+      <c r="Z6" s="67"/>
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="67"/>
+      <c r="AD6" s="67"/>
+      <c r="AE6" s="67"/>
+      <c r="AF6" s="67"/>
+      <c r="AG6" s="68"/>
+      <c r="AH6" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="AI6" s="38"/>
-      <c r="AJ6" s="38"/>
-      <c r="AK6" s="38"/>
-      <c r="AL6" s="38"/>
-      <c r="AM6" s="39"/>
-      <c r="AN6" s="45"/>
-      <c r="AO6" s="38"/>
-      <c r="AP6" s="38"/>
-      <c r="AQ6" s="38"/>
-      <c r="AR6" s="38"/>
-      <c r="AS6" s="38"/>
-      <c r="AT6" s="38"/>
-      <c r="AU6" s="38"/>
-      <c r="AV6" s="38"/>
-      <c r="AW6" s="38"/>
-      <c r="AX6" s="38"/>
-      <c r="AY6" s="38"/>
-      <c r="AZ6" s="38"/>
-      <c r="BA6" s="39"/>
+      <c r="AI6" s="35"/>
+      <c r="AJ6" s="35"/>
+      <c r="AK6" s="35"/>
+      <c r="AL6" s="35"/>
+      <c r="AM6" s="36"/>
+      <c r="AN6" s="55"/>
+      <c r="AO6" s="35"/>
+      <c r="AP6" s="35"/>
+      <c r="AQ6" s="35"/>
+      <c r="AR6" s="35"/>
+      <c r="AS6" s="35"/>
+      <c r="AT6" s="35"/>
+      <c r="AU6" s="35"/>
+      <c r="AV6" s="35"/>
+      <c r="AW6" s="35"/>
+      <c r="AX6" s="35"/>
+      <c r="AY6" s="35"/>
+      <c r="AZ6" s="35"/>
+      <c r="BA6" s="36"/>
     </row>
     <row r="7" spans="1:56">
-      <c r="B7" s="40"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="55"/>
-      <c r="N7" s="55"/>
-      <c r="O7" s="55"/>
-      <c r="P7" s="55"/>
-      <c r="Q7" s="55"/>
-      <c r="R7" s="55"/>
-      <c r="S7" s="55"/>
-      <c r="T7" s="55"/>
-      <c r="U7" s="55"/>
-      <c r="V7" s="55"/>
-      <c r="W7" s="55"/>
-      <c r="X7" s="55"/>
-      <c r="Y7" s="55"/>
-      <c r="Z7" s="55"/>
-      <c r="AA7" s="55"/>
-      <c r="AB7" s="55"/>
-      <c r="AC7" s="55"/>
-      <c r="AD7" s="55"/>
-      <c r="AE7" s="55"/>
-      <c r="AF7" s="55"/>
-      <c r="AG7" s="56"/>
-      <c r="AH7" s="40"/>
-      <c r="AI7" s="41"/>
-      <c r="AJ7" s="41"/>
-      <c r="AK7" s="41"/>
-      <c r="AL7" s="41"/>
-      <c r="AM7" s="42"/>
-      <c r="AN7" s="40"/>
-      <c r="AO7" s="41"/>
-      <c r="AP7" s="41"/>
-      <c r="AQ7" s="41"/>
-      <c r="AR7" s="41"/>
-      <c r="AS7" s="41"/>
-      <c r="AT7" s="41"/>
-      <c r="AU7" s="41"/>
-      <c r="AV7" s="41"/>
-      <c r="AW7" s="41"/>
-      <c r="AX7" s="41"/>
-      <c r="AY7" s="41"/>
-      <c r="AZ7" s="41"/>
-      <c r="BA7" s="42"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="70"/>
+      <c r="M7" s="70"/>
+      <c r="N7" s="70"/>
+      <c r="O7" s="70"/>
+      <c r="P7" s="70"/>
+      <c r="Q7" s="70"/>
+      <c r="R7" s="70"/>
+      <c r="S7" s="70"/>
+      <c r="T7" s="70"/>
+      <c r="U7" s="70"/>
+      <c r="V7" s="70"/>
+      <c r="W7" s="70"/>
+      <c r="X7" s="70"/>
+      <c r="Y7" s="70"/>
+      <c r="Z7" s="70"/>
+      <c r="AA7" s="70"/>
+      <c r="AB7" s="70"/>
+      <c r="AC7" s="70"/>
+      <c r="AD7" s="70"/>
+      <c r="AE7" s="70"/>
+      <c r="AF7" s="70"/>
+      <c r="AG7" s="71"/>
+      <c r="AH7" s="38"/>
+      <c r="AI7" s="39"/>
+      <c r="AJ7" s="39"/>
+      <c r="AK7" s="39"/>
+      <c r="AL7" s="39"/>
+      <c r="AM7" s="40"/>
+      <c r="AN7" s="38"/>
+      <c r="AO7" s="39"/>
+      <c r="AP7" s="39"/>
+      <c r="AQ7" s="39"/>
+      <c r="AR7" s="39"/>
+      <c r="AS7" s="39"/>
+      <c r="AT7" s="39"/>
+      <c r="AU7" s="39"/>
+      <c r="AV7" s="39"/>
+      <c r="AW7" s="39"/>
+      <c r="AX7" s="39"/>
+      <c r="AY7" s="39"/>
+      <c r="AZ7" s="39"/>
+      <c r="BA7" s="40"/>
     </row>
     <row r="8" spans="1:56">
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="38"/>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="38"/>
-      <c r="R8" s="38"/>
-      <c r="S8" s="38"/>
-      <c r="T8" s="38"/>
-      <c r="U8" s="38"/>
-      <c r="V8" s="38"/>
-      <c r="W8" s="38"/>
-      <c r="X8" s="38"/>
-      <c r="Y8" s="38"/>
-      <c r="Z8" s="38"/>
-      <c r="AA8" s="38"/>
-      <c r="AB8" s="38"/>
-      <c r="AC8" s="38"/>
-      <c r="AD8" s="38"/>
-      <c r="AE8" s="38"/>
-      <c r="AF8" s="38"/>
-      <c r="AG8" s="39"/>
-      <c r="AH8" s="43" t="s">
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="35"/>
+      <c r="S8" s="35"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="35"/>
+      <c r="V8" s="35"/>
+      <c r="W8" s="35"/>
+      <c r="X8" s="35"/>
+      <c r="Y8" s="35"/>
+      <c r="Z8" s="35"/>
+      <c r="AA8" s="35"/>
+      <c r="AB8" s="35"/>
+      <c r="AC8" s="35"/>
+      <c r="AD8" s="35"/>
+      <c r="AE8" s="35"/>
+      <c r="AF8" s="35"/>
+      <c r="AG8" s="36"/>
+      <c r="AH8" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AI8" s="38"/>
-      <c r="AJ8" s="38"/>
-      <c r="AK8" s="38"/>
-      <c r="AL8" s="38"/>
-      <c r="AM8" s="39"/>
-      <c r="AN8" s="60"/>
-      <c r="AO8" s="38"/>
-      <c r="AP8" s="38"/>
-      <c r="AQ8" s="38"/>
-      <c r="AR8" s="38"/>
-      <c r="AS8" s="38"/>
-      <c r="AT8" s="38"/>
-      <c r="AU8" s="38"/>
-      <c r="AV8" s="38"/>
-      <c r="AW8" s="38"/>
-      <c r="AX8" s="38"/>
-      <c r="AY8" s="38"/>
-      <c r="AZ8" s="38"/>
-      <c r="BA8" s="39"/>
+      <c r="AI8" s="35"/>
+      <c r="AJ8" s="35"/>
+      <c r="AK8" s="35"/>
+      <c r="AL8" s="35"/>
+      <c r="AM8" s="36"/>
+      <c r="AN8" s="37"/>
+      <c r="AO8" s="35"/>
+      <c r="AP8" s="35"/>
+      <c r="AQ8" s="35"/>
+      <c r="AR8" s="35"/>
+      <c r="AS8" s="35"/>
+      <c r="AT8" s="35"/>
+      <c r="AU8" s="35"/>
+      <c r="AV8" s="35"/>
+      <c r="AW8" s="35"/>
+      <c r="AX8" s="35"/>
+      <c r="AY8" s="35"/>
+      <c r="AZ8" s="35"/>
+      <c r="BA8" s="36"/>
     </row>
     <row r="9" spans="1:56">
-      <c r="B9" s="40"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="41"/>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="41"/>
-      <c r="S9" s="41"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="41"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="41"/>
-      <c r="X9" s="41"/>
-      <c r="Y9" s="41"/>
-      <c r="Z9" s="41"/>
-      <c r="AA9" s="41"/>
-      <c r="AB9" s="41"/>
-      <c r="AC9" s="41"/>
-      <c r="AD9" s="41"/>
-      <c r="AE9" s="41"/>
-      <c r="AF9" s="41"/>
-      <c r="AG9" s="42"/>
-      <c r="AH9" s="40"/>
-      <c r="AI9" s="41"/>
-      <c r="AJ9" s="41"/>
-      <c r="AK9" s="41"/>
-      <c r="AL9" s="41"/>
-      <c r="AM9" s="42"/>
-      <c r="AN9" s="40"/>
-      <c r="AO9" s="41"/>
-      <c r="AP9" s="41"/>
-      <c r="AQ9" s="41"/>
-      <c r="AR9" s="41"/>
-      <c r="AS9" s="41"/>
-      <c r="AT9" s="41"/>
-      <c r="AU9" s="41"/>
-      <c r="AV9" s="41"/>
-      <c r="AW9" s="41"/>
-      <c r="AX9" s="41"/>
-      <c r="AY9" s="41"/>
-      <c r="AZ9" s="41"/>
-      <c r="BA9" s="42"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="39"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="39"/>
+      <c r="P9" s="39"/>
+      <c r="Q9" s="39"/>
+      <c r="R9" s="39"/>
+      <c r="S9" s="39"/>
+      <c r="T9" s="39"/>
+      <c r="U9" s="39"/>
+      <c r="V9" s="39"/>
+      <c r="W9" s="39"/>
+      <c r="X9" s="39"/>
+      <c r="Y9" s="39"/>
+      <c r="Z9" s="39"/>
+      <c r="AA9" s="39"/>
+      <c r="AB9" s="39"/>
+      <c r="AC9" s="39"/>
+      <c r="AD9" s="39"/>
+      <c r="AE9" s="39"/>
+      <c r="AF9" s="39"/>
+      <c r="AG9" s="40"/>
+      <c r="AH9" s="38"/>
+      <c r="AI9" s="39"/>
+      <c r="AJ9" s="39"/>
+      <c r="AK9" s="39"/>
+      <c r="AL9" s="39"/>
+      <c r="AM9" s="40"/>
+      <c r="AN9" s="38"/>
+      <c r="AO9" s="39"/>
+      <c r="AP9" s="39"/>
+      <c r="AQ9" s="39"/>
+      <c r="AR9" s="39"/>
+      <c r="AS9" s="39"/>
+      <c r="AT9" s="39"/>
+      <c r="AU9" s="39"/>
+      <c r="AV9" s="39"/>
+      <c r="AW9" s="39"/>
+      <c r="AX9" s="39"/>
+      <c r="AY9" s="39"/>
+      <c r="AZ9" s="39"/>
+      <c r="BA9" s="40"/>
     </row>
     <row r="10" spans="1:56">
       <c r="B10" s="8"/>
@@ -1768,28 +1823,28 @@
       <c r="AE10" s="8"/>
       <c r="AF10" s="8"/>
       <c r="AG10" s="8"/>
-      <c r="AH10" s="37" t="s">
-        <v>18</v>
+      <c r="AH10" s="45" t="s">
+        <v>17</v>
       </c>
-      <c r="AI10" s="38"/>
-      <c r="AJ10" s="38"/>
-      <c r="AK10" s="38"/>
-      <c r="AL10" s="38"/>
-      <c r="AM10" s="39"/>
-      <c r="AN10" s="76"/>
-      <c r="AO10" s="77"/>
-      <c r="AP10" s="77"/>
-      <c r="AQ10" s="77"/>
-      <c r="AR10" s="77"/>
-      <c r="AS10" s="77"/>
-      <c r="AT10" s="77"/>
-      <c r="AU10" s="77"/>
-      <c r="AV10" s="77"/>
-      <c r="AW10" s="77"/>
-      <c r="AX10" s="77"/>
-      <c r="AY10" s="77"/>
-      <c r="AZ10" s="77"/>
-      <c r="BA10" s="78"/>
+      <c r="AI10" s="35"/>
+      <c r="AJ10" s="35"/>
+      <c r="AK10" s="35"/>
+      <c r="AL10" s="35"/>
+      <c r="AM10" s="36"/>
+      <c r="AN10" s="56"/>
+      <c r="AO10" s="57"/>
+      <c r="AP10" s="57"/>
+      <c r="AQ10" s="57"/>
+      <c r="AR10" s="57"/>
+      <c r="AS10" s="57"/>
+      <c r="AT10" s="57"/>
+      <c r="AU10" s="57"/>
+      <c r="AV10" s="57"/>
+      <c r="AW10" s="57"/>
+      <c r="AX10" s="57"/>
+      <c r="AY10" s="57"/>
+      <c r="AZ10" s="57"/>
+      <c r="BA10" s="58"/>
     </row>
     <row r="11" spans="1:56">
       <c r="B11" s="11"/>
@@ -1824,124 +1879,124 @@
       <c r="AE11" s="8"/>
       <c r="AF11" s="8"/>
       <c r="AG11" s="8"/>
-      <c r="AH11" s="40"/>
-      <c r="AI11" s="41"/>
-      <c r="AJ11" s="41"/>
-      <c r="AK11" s="41"/>
-      <c r="AL11" s="41"/>
-      <c r="AM11" s="42"/>
-      <c r="AN11" s="79"/>
-      <c r="AO11" s="80"/>
-      <c r="AP11" s="80"/>
-      <c r="AQ11" s="80"/>
-      <c r="AR11" s="80"/>
-      <c r="AS11" s="80"/>
-      <c r="AT11" s="80"/>
-      <c r="AU11" s="80"/>
-      <c r="AV11" s="80"/>
-      <c r="AW11" s="80"/>
-      <c r="AX11" s="80"/>
-      <c r="AY11" s="80"/>
-      <c r="AZ11" s="80"/>
-      <c r="BA11" s="81"/>
+      <c r="AH11" s="38"/>
+      <c r="AI11" s="39"/>
+      <c r="AJ11" s="39"/>
+      <c r="AK11" s="39"/>
+      <c r="AL11" s="39"/>
+      <c r="AM11" s="40"/>
+      <c r="AN11" s="59"/>
+      <c r="AO11" s="60"/>
+      <c r="AP11" s="60"/>
+      <c r="AQ11" s="60"/>
+      <c r="AR11" s="60"/>
+      <c r="AS11" s="60"/>
+      <c r="AT11" s="60"/>
+      <c r="AU11" s="60"/>
+      <c r="AV11" s="60"/>
+      <c r="AW11" s="60"/>
+      <c r="AX11" s="60"/>
+      <c r="AY11" s="60"/>
+      <c r="AZ11" s="60"/>
+      <c r="BA11" s="61"/>
     </row>
     <row r="12" spans="1:56">
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="39"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="35"/>
+      <c r="Q12" s="35"/>
+      <c r="R12" s="35"/>
+      <c r="S12" s="35"/>
+      <c r="T12" s="35"/>
+      <c r="U12" s="36"/>
       <c r="AC12" s="8"/>
       <c r="AD12" s="8"/>
       <c r="AE12" s="8"/>
       <c r="AF12" s="8"/>
       <c r="AG12" s="8"/>
-      <c r="AH12" s="37" t="s">
-        <v>19</v>
+      <c r="AH12" s="45" t="s">
+        <v>18</v>
       </c>
-      <c r="AI12" s="38"/>
-      <c r="AJ12" s="38"/>
-      <c r="AK12" s="38"/>
-      <c r="AL12" s="38"/>
-      <c r="AM12" s="39"/>
-      <c r="AN12" s="76"/>
-      <c r="AO12" s="77"/>
-      <c r="AP12" s="77"/>
-      <c r="AQ12" s="77"/>
-      <c r="AR12" s="77"/>
-      <c r="AS12" s="77"/>
-      <c r="AT12" s="77"/>
-      <c r="AU12" s="77"/>
-      <c r="AV12" s="77"/>
-      <c r="AW12" s="77"/>
-      <c r="AX12" s="77"/>
-      <c r="AY12" s="77"/>
-      <c r="AZ12" s="77"/>
-      <c r="BA12" s="78"/>
+      <c r="AI12" s="35"/>
+      <c r="AJ12" s="35"/>
+      <c r="AK12" s="35"/>
+      <c r="AL12" s="35"/>
+      <c r="AM12" s="36"/>
+      <c r="AN12" s="56"/>
+      <c r="AO12" s="57"/>
+      <c r="AP12" s="57"/>
+      <c r="AQ12" s="57"/>
+      <c r="AR12" s="57"/>
+      <c r="AS12" s="57"/>
+      <c r="AT12" s="57"/>
+      <c r="AU12" s="57"/>
+      <c r="AV12" s="57"/>
+      <c r="AW12" s="57"/>
+      <c r="AX12" s="57"/>
+      <c r="AY12" s="57"/>
+      <c r="AZ12" s="57"/>
+      <c r="BA12" s="58"/>
     </row>
     <row r="13" spans="1:56">
-      <c r="B13" s="40"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
-      <c r="N13" s="41"/>
-      <c r="O13" s="41"/>
-      <c r="P13" s="41"/>
-      <c r="Q13" s="41"/>
-      <c r="R13" s="41"/>
-      <c r="S13" s="41"/>
-      <c r="T13" s="41"/>
-      <c r="U13" s="42"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="39"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="39"/>
+      <c r="P13" s="39"/>
+      <c r="Q13" s="39"/>
+      <c r="R13" s="39"/>
+      <c r="S13" s="39"/>
+      <c r="T13" s="39"/>
+      <c r="U13" s="40"/>
       <c r="AC13" s="8"/>
       <c r="AD13" s="8"/>
       <c r="AE13" s="8"/>
       <c r="AF13" s="8"/>
       <c r="AG13" s="8"/>
-      <c r="AH13" s="40"/>
-      <c r="AI13" s="41"/>
-      <c r="AJ13" s="41"/>
-      <c r="AK13" s="41"/>
-      <c r="AL13" s="41"/>
-      <c r="AM13" s="42"/>
-      <c r="AN13" s="79"/>
-      <c r="AO13" s="80"/>
-      <c r="AP13" s="80"/>
-      <c r="AQ13" s="80"/>
-      <c r="AR13" s="80"/>
-      <c r="AS13" s="80"/>
-      <c r="AT13" s="80"/>
-      <c r="AU13" s="80"/>
-      <c r="AV13" s="80"/>
-      <c r="AW13" s="80"/>
-      <c r="AX13" s="80"/>
-      <c r="AY13" s="80"/>
-      <c r="AZ13" s="80"/>
-      <c r="BA13" s="81"/>
+      <c r="AH13" s="38"/>
+      <c r="AI13" s="39"/>
+      <c r="AJ13" s="39"/>
+      <c r="AK13" s="39"/>
+      <c r="AL13" s="39"/>
+      <c r="AM13" s="40"/>
+      <c r="AN13" s="59"/>
+      <c r="AO13" s="60"/>
+      <c r="AP13" s="60"/>
+      <c r="AQ13" s="60"/>
+      <c r="AR13" s="60"/>
+      <c r="AS13" s="60"/>
+      <c r="AT13" s="60"/>
+      <c r="AU13" s="60"/>
+      <c r="AV13" s="60"/>
+      <c r="AW13" s="60"/>
+      <c r="AX13" s="60"/>
+      <c r="AY13" s="60"/>
+      <c r="AZ13" s="60"/>
+      <c r="BA13" s="61"/>
     </row>
     <row r="14" spans="1:56">
       <c r="B14" s="8"/>
@@ -1999,7 +2054,7 @@
     </row>
     <row r="15" spans="1:56">
       <c r="B15" s="11" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -2054,110 +2109,110 @@
       <c r="BA15" s="8"/>
     </row>
     <row r="16" spans="1:56" ht="24" customHeight="1">
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="49" t="s">
+      <c r="B16" s="80" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="81"/>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="81"/>
+      <c r="I16" s="81"/>
+      <c r="J16" s="81"/>
+      <c r="K16" s="84"/>
+      <c r="L16" s="85"/>
+      <c r="M16" s="85"/>
+      <c r="N16" s="85"/>
+      <c r="O16" s="85"/>
+      <c r="P16" s="86"/>
+      <c r="Q16" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="38"/>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="44" t="s">
+      <c r="R16" s="35"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="35"/>
+      <c r="U16" s="35"/>
+      <c r="V16" s="35"/>
+      <c r="W16" s="35"/>
+      <c r="X16" s="35"/>
+      <c r="Y16" s="35"/>
+      <c r="Z16" s="35"/>
+      <c r="AA16" s="35"/>
+      <c r="AB16" s="65"/>
+      <c r="AC16" s="35"/>
+      <c r="AD16" s="35"/>
+      <c r="AE16" s="35"/>
+      <c r="AF16" s="35"/>
+      <c r="AG16" s="35"/>
+      <c r="AH16" s="35"/>
+      <c r="AI16" s="35"/>
+      <c r="AJ16" s="36"/>
+      <c r="AK16" s="46" t="s">
         <v>9</v>
-      </c>
-      <c r="R16" s="38"/>
-      <c r="S16" s="38"/>
-      <c r="T16" s="38"/>
-      <c r="U16" s="38"/>
-      <c r="V16" s="38"/>
-      <c r="W16" s="38"/>
-      <c r="X16" s="38"/>
-      <c r="Y16" s="38"/>
-      <c r="Z16" s="38"/>
-      <c r="AA16" s="38"/>
-      <c r="AB16" s="46"/>
-      <c r="AC16" s="38"/>
-      <c r="AD16" s="38"/>
-      <c r="AE16" s="38"/>
-      <c r="AF16" s="38"/>
-      <c r="AG16" s="38"/>
-      <c r="AH16" s="38"/>
-      <c r="AI16" s="38"/>
-      <c r="AJ16" s="39"/>
-      <c r="AK16" s="62" t="s">
-        <v>10</v>
       </c>
       <c r="AL16" s="47"/>
       <c r="AM16" s="47"/>
       <c r="AN16" s="47"/>
       <c r="AO16" s="47"/>
       <c r="AP16" s="48"/>
-      <c r="AQ16" s="59"/>
-      <c r="AR16" s="38"/>
-      <c r="AS16" s="38"/>
-      <c r="AT16" s="38"/>
-      <c r="AU16" s="38"/>
-      <c r="AV16" s="38"/>
-      <c r="AW16" s="38"/>
-      <c r="AX16" s="38"/>
-      <c r="AY16" s="38"/>
-      <c r="AZ16" s="38"/>
-      <c r="BA16" s="39"/>
+      <c r="AQ16" s="34"/>
+      <c r="AR16" s="35"/>
+      <c r="AS16" s="35"/>
+      <c r="AT16" s="35"/>
+      <c r="AU16" s="35"/>
+      <c r="AV16" s="35"/>
+      <c r="AW16" s="35"/>
+      <c r="AX16" s="35"/>
+      <c r="AY16" s="35"/>
+      <c r="AZ16" s="35"/>
+      <c r="BA16" s="36"/>
     </row>
     <row r="17" spans="2:53" ht="24" customHeight="1">
-      <c r="B17" s="40"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
-      <c r="K17" s="41"/>
-      <c r="L17" s="41"/>
-      <c r="M17" s="41"/>
-      <c r="N17" s="41"/>
-      <c r="O17" s="41"/>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="40"/>
-      <c r="R17" s="41"/>
-      <c r="S17" s="41"/>
-      <c r="T17" s="41"/>
-      <c r="U17" s="41"/>
-      <c r="V17" s="41"/>
-      <c r="W17" s="41"/>
-      <c r="X17" s="41"/>
-      <c r="Y17" s="41"/>
-      <c r="Z17" s="41"/>
-      <c r="AA17" s="41"/>
-      <c r="AB17" s="40"/>
-      <c r="AC17" s="41"/>
-      <c r="AD17" s="41"/>
-      <c r="AE17" s="41"/>
-      <c r="AF17" s="41"/>
-      <c r="AG17" s="41"/>
-      <c r="AH17" s="41"/>
-      <c r="AI17" s="41"/>
-      <c r="AJ17" s="42"/>
-      <c r="AK17" s="63" t="s">
-        <v>11</v>
+      <c r="B17" s="82"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="83"/>
+      <c r="H17" s="83"/>
+      <c r="I17" s="83"/>
+      <c r="J17" s="83"/>
+      <c r="K17" s="87"/>
+      <c r="L17" s="88"/>
+      <c r="M17" s="88"/>
+      <c r="N17" s="88"/>
+      <c r="O17" s="88"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="38"/>
+      <c r="R17" s="39"/>
+      <c r="S17" s="39"/>
+      <c r="T17" s="39"/>
+      <c r="U17" s="39"/>
+      <c r="V17" s="39"/>
+      <c r="W17" s="39"/>
+      <c r="X17" s="39"/>
+      <c r="Y17" s="39"/>
+      <c r="Z17" s="39"/>
+      <c r="AA17" s="39"/>
+      <c r="AB17" s="38"/>
+      <c r="AC17" s="39"/>
+      <c r="AD17" s="39"/>
+      <c r="AE17" s="39"/>
+      <c r="AF17" s="39"/>
+      <c r="AG17" s="39"/>
+      <c r="AH17" s="39"/>
+      <c r="AI17" s="39"/>
+      <c r="AJ17" s="40"/>
+      <c r="AK17" s="49" t="s">
+        <v>10</v>
       </c>
-      <c r="AL17" s="41"/>
-      <c r="AM17" s="41"/>
-      <c r="AN17" s="41"/>
-      <c r="AO17" s="41"/>
-      <c r="AP17" s="42"/>
-      <c r="AQ17" s="46"/>
+      <c r="AL17" s="39"/>
+      <c r="AM17" s="39"/>
+      <c r="AN17" s="39"/>
+      <c r="AO17" s="39"/>
+      <c r="AP17" s="40"/>
+      <c r="AQ17" s="65"/>
       <c r="AR17" s="47"/>
       <c r="AS17" s="47"/>
       <c r="AT17" s="47"/>
@@ -2170,450 +2225,461 @@
       <c r="BA17" s="48"/>
     </row>
     <row r="18" spans="2:53" ht="13.5" customHeight="1">
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="50" t="s">
-        <v>12</v>
+      <c r="B18" s="90" t="s">
+        <v>11</v>
       </c>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="38"/>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="64" t="s">
+      <c r="C18" s="91"/>
+      <c r="D18" s="91"/>
+      <c r="E18" s="91"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="91"/>
+      <c r="H18" s="91"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="91"/>
+      <c r="K18" s="91"/>
+      <c r="L18" s="91"/>
+      <c r="M18" s="91"/>
+      <c r="N18" s="91"/>
+      <c r="O18" s="91"/>
+      <c r="P18" s="92"/>
+      <c r="Q18" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="R18" s="52"/>
+      <c r="S18" s="52"/>
+      <c r="T18" s="52"/>
+      <c r="U18" s="52"/>
+      <c r="V18" s="52"/>
+      <c r="W18" s="52"/>
+      <c r="X18" s="52"/>
+      <c r="Y18" s="52"/>
+      <c r="Z18" s="52"/>
+      <c r="AA18" s="52"/>
+      <c r="AB18" s="52"/>
+      <c r="AC18" s="52"/>
+      <c r="AD18" s="52"/>
+      <c r="AE18" s="52"/>
+      <c r="AF18" s="52"/>
+      <c r="AG18" s="52"/>
+      <c r="AH18" s="52"/>
+      <c r="AI18" s="62" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ18" s="62"/>
+      <c r="AK18" s="62"/>
+      <c r="AL18" s="62"/>
+      <c r="AM18" s="62"/>
+      <c r="AN18" s="62"/>
+      <c r="AO18" s="62"/>
+      <c r="AP18" s="62"/>
+      <c r="AQ18" s="62"/>
+      <c r="AR18" s="62"/>
+      <c r="AS18" s="62"/>
+      <c r="AT18" s="62"/>
+      <c r="AU18" s="62"/>
+      <c r="AV18" s="62"/>
+      <c r="AW18" s="62"/>
+      <c r="AX18" s="62"/>
+      <c r="AY18" s="62"/>
+      <c r="AZ18" s="62"/>
+      <c r="BA18" s="62"/>
+    </row>
+    <row r="19" spans="2:53">
+      <c r="B19" s="93"/>
+      <c r="C19" s="94"/>
+      <c r="D19" s="94"/>
+      <c r="E19" s="94"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="94"/>
+      <c r="H19" s="94"/>
+      <c r="I19" s="94"/>
+      <c r="J19" s="94"/>
+      <c r="K19" s="94"/>
+      <c r="L19" s="94"/>
+      <c r="M19" s="94"/>
+      <c r="N19" s="94"/>
+      <c r="O19" s="94"/>
+      <c r="P19" s="95"/>
+      <c r="Q19" s="53"/>
+      <c r="R19" s="54"/>
+      <c r="S19" s="54"/>
+      <c r="T19" s="54"/>
+      <c r="U19" s="54"/>
+      <c r="V19" s="54"/>
+      <c r="W19" s="54"/>
+      <c r="X19" s="54"/>
+      <c r="Y19" s="54"/>
+      <c r="Z19" s="54"/>
+      <c r="AA19" s="54"/>
+      <c r="AB19" s="54"/>
+      <c r="AC19" s="54"/>
+      <c r="AD19" s="54"/>
+      <c r="AE19" s="54"/>
+      <c r="AF19" s="54"/>
+      <c r="AG19" s="54"/>
+      <c r="AH19" s="54"/>
+      <c r="AI19" s="62"/>
+      <c r="AJ19" s="62"/>
+      <c r="AK19" s="62"/>
+      <c r="AL19" s="62"/>
+      <c r="AM19" s="62"/>
+      <c r="AN19" s="62"/>
+      <c r="AO19" s="62"/>
+      <c r="AP19" s="62"/>
+      <c r="AQ19" s="62"/>
+      <c r="AR19" s="62"/>
+      <c r="AS19" s="62"/>
+      <c r="AT19" s="62"/>
+      <c r="AU19" s="62"/>
+      <c r="AV19" s="62"/>
+      <c r="AW19" s="62"/>
+      <c r="AX19" s="62"/>
+      <c r="AY19" s="62"/>
+      <c r="AZ19" s="62"/>
+      <c r="BA19" s="62"/>
+    </row>
+    <row r="22" spans="2:53">
+      <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R18" s="65"/>
-      <c r="S18" s="65"/>
-      <c r="T18" s="65"/>
-      <c r="U18" s="65"/>
-      <c r="V18" s="65"/>
-      <c r="W18" s="65"/>
-      <c r="X18" s="65"/>
-      <c r="Y18" s="65"/>
-      <c r="Z18" s="65"/>
-      <c r="AA18" s="65"/>
-      <c r="AB18" s="65"/>
-      <c r="AC18" s="65"/>
-      <c r="AD18" s="65"/>
-      <c r="AE18" s="65"/>
-      <c r="AF18" s="65"/>
-      <c r="AG18" s="65"/>
-      <c r="AH18" s="65"/>
-      <c r="AI18" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="AJ18" s="34"/>
-      <c r="AK18" s="34"/>
-      <c r="AL18" s="34"/>
-      <c r="AM18" s="34"/>
-      <c r="AN18" s="34"/>
-      <c r="AO18" s="34"/>
-      <c r="AP18" s="34"/>
-      <c r="AQ18" s="34"/>
-      <c r="AR18" s="34"/>
-      <c r="AS18" s="34"/>
-      <c r="AT18" s="34"/>
-      <c r="AU18" s="34"/>
-      <c r="AV18" s="34"/>
-      <c r="AW18" s="34"/>
-      <c r="AX18" s="34"/>
-      <c r="AY18" s="34"/>
-      <c r="AZ18" s="34"/>
-      <c r="BA18" s="34"/>
-    </row>
-    <row r="19" spans="2:53">
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="41"/>
-      <c r="M19" s="41"/>
-      <c r="N19" s="41"/>
-      <c r="O19" s="41"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="66"/>
-      <c r="R19" s="67"/>
-      <c r="S19" s="67"/>
-      <c r="T19" s="67"/>
-      <c r="U19" s="67"/>
-      <c r="V19" s="67"/>
-      <c r="W19" s="67"/>
-      <c r="X19" s="67"/>
-      <c r="Y19" s="67"/>
-      <c r="Z19" s="67"/>
-      <c r="AA19" s="67"/>
-      <c r="AB19" s="67"/>
-      <c r="AC19" s="67"/>
-      <c r="AD19" s="67"/>
-      <c r="AE19" s="67"/>
-      <c r="AF19" s="67"/>
-      <c r="AG19" s="67"/>
-      <c r="AH19" s="67"/>
-      <c r="AI19" s="34"/>
-      <c r="AJ19" s="34"/>
-      <c r="AK19" s="34"/>
-      <c r="AL19" s="34"/>
-      <c r="AM19" s="34"/>
-      <c r="AN19" s="34"/>
-      <c r="AO19" s="34"/>
-      <c r="AP19" s="34"/>
-      <c r="AQ19" s="34"/>
-      <c r="AR19" s="34"/>
-      <c r="AS19" s="34"/>
-      <c r="AT19" s="34"/>
-      <c r="AU19" s="34"/>
-      <c r="AV19" s="34"/>
-      <c r="AW19" s="34"/>
-      <c r="AX19" s="34"/>
-      <c r="AY19" s="34"/>
-      <c r="AZ19" s="34"/>
-      <c r="BA19" s="34"/>
-    </row>
-    <row r="22" spans="2:53">
-      <c r="B22" s="2" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="23" spans="2:53">
-      <c r="B23" s="61"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="38"/>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="38"/>
-      <c r="R23" s="38"/>
-      <c r="S23" s="38"/>
-      <c r="T23" s="38"/>
-      <c r="U23" s="38"/>
-      <c r="V23" s="38"/>
-      <c r="W23" s="38"/>
-      <c r="X23" s="38"/>
-      <c r="Y23" s="38"/>
-      <c r="Z23" s="38"/>
-      <c r="AA23" s="38"/>
-      <c r="AB23" s="38"/>
-      <c r="AC23" s="38"/>
-      <c r="AD23" s="38"/>
-      <c r="AE23" s="38"/>
-      <c r="AF23" s="38"/>
-      <c r="AG23" s="38"/>
-      <c r="AH23" s="38"/>
-      <c r="AI23" s="38"/>
-      <c r="AJ23" s="38"/>
-      <c r="AK23" s="38"/>
-      <c r="AL23" s="38"/>
-      <c r="AM23" s="38"/>
-      <c r="AN23" s="38"/>
-      <c r="AO23" s="38"/>
-      <c r="AP23" s="38"/>
-      <c r="AQ23" s="38"/>
-      <c r="AR23" s="38"/>
-      <c r="AS23" s="38"/>
-      <c r="AT23" s="38"/>
-      <c r="AU23" s="38"/>
-      <c r="AV23" s="38"/>
-      <c r="AW23" s="38"/>
-      <c r="AX23" s="38"/>
-      <c r="AY23" s="38"/>
-      <c r="AZ23" s="38"/>
-      <c r="BA23" s="39"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="35"/>
+      <c r="S23" s="35"/>
+      <c r="T23" s="35"/>
+      <c r="U23" s="35"/>
+      <c r="V23" s="35"/>
+      <c r="W23" s="35"/>
+      <c r="X23" s="35"/>
+      <c r="Y23" s="35"/>
+      <c r="Z23" s="35"/>
+      <c r="AA23" s="35"/>
+      <c r="AB23" s="35"/>
+      <c r="AC23" s="35"/>
+      <c r="AD23" s="35"/>
+      <c r="AE23" s="35"/>
+      <c r="AF23" s="35"/>
+      <c r="AG23" s="35"/>
+      <c r="AH23" s="35"/>
+      <c r="AI23" s="35"/>
+      <c r="AJ23" s="35"/>
+      <c r="AK23" s="35"/>
+      <c r="AL23" s="35"/>
+      <c r="AM23" s="35"/>
+      <c r="AN23" s="35"/>
+      <c r="AO23" s="35"/>
+      <c r="AP23" s="35"/>
+      <c r="AQ23" s="35"/>
+      <c r="AR23" s="35"/>
+      <c r="AS23" s="35"/>
+      <c r="AT23" s="35"/>
+      <c r="AU23" s="35"/>
+      <c r="AV23" s="35"/>
+      <c r="AW23" s="35"/>
+      <c r="AX23" s="35"/>
+      <c r="AY23" s="35"/>
+      <c r="AZ23" s="35"/>
+      <c r="BA23" s="36"/>
     </row>
     <row r="24" spans="2:53">
-      <c r="B24" s="57"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="36"/>
-      <c r="K24" s="36"/>
-      <c r="L24" s="36"/>
-      <c r="M24" s="36"/>
-      <c r="N24" s="36"/>
-      <c r="O24" s="36"/>
-      <c r="P24" s="36"/>
-      <c r="Q24" s="36"/>
-      <c r="R24" s="36"/>
-      <c r="S24" s="36"/>
-      <c r="T24" s="36"/>
-      <c r="U24" s="36"/>
-      <c r="V24" s="36"/>
-      <c r="W24" s="36"/>
-      <c r="X24" s="36"/>
-      <c r="Y24" s="36"/>
-      <c r="Z24" s="36"/>
-      <c r="AA24" s="36"/>
-      <c r="AB24" s="36"/>
-      <c r="AC24" s="36"/>
-      <c r="AD24" s="36"/>
-      <c r="AE24" s="36"/>
-      <c r="AF24" s="36"/>
-      <c r="AG24" s="36"/>
-      <c r="AH24" s="36"/>
-      <c r="AI24" s="36"/>
-      <c r="AJ24" s="36"/>
-      <c r="AK24" s="36"/>
-      <c r="AL24" s="36"/>
-      <c r="AM24" s="36"/>
-      <c r="AN24" s="36"/>
-      <c r="AO24" s="36"/>
-      <c r="AP24" s="36"/>
-      <c r="AQ24" s="36"/>
-      <c r="AR24" s="36"/>
-      <c r="AS24" s="36"/>
-      <c r="AT24" s="36"/>
-      <c r="AU24" s="36"/>
-      <c r="AV24" s="36"/>
-      <c r="AW24" s="36"/>
-      <c r="AX24" s="36"/>
-      <c r="AY24" s="36"/>
-      <c r="AZ24" s="36"/>
-      <c r="BA24" s="58"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="43"/>
+      <c r="M24" s="43"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="43"/>
+      <c r="P24" s="43"/>
+      <c r="Q24" s="43"/>
+      <c r="R24" s="43"/>
+      <c r="S24" s="43"/>
+      <c r="T24" s="43"/>
+      <c r="U24" s="43"/>
+      <c r="V24" s="43"/>
+      <c r="W24" s="43"/>
+      <c r="X24" s="43"/>
+      <c r="Y24" s="43"/>
+      <c r="Z24" s="43"/>
+      <c r="AA24" s="43"/>
+      <c r="AB24" s="43"/>
+      <c r="AC24" s="43"/>
+      <c r="AD24" s="43"/>
+      <c r="AE24" s="43"/>
+      <c r="AF24" s="43"/>
+      <c r="AG24" s="43"/>
+      <c r="AH24" s="43"/>
+      <c r="AI24" s="43"/>
+      <c r="AJ24" s="43"/>
+      <c r="AK24" s="43"/>
+      <c r="AL24" s="43"/>
+      <c r="AM24" s="43"/>
+      <c r="AN24" s="43"/>
+      <c r="AO24" s="43"/>
+      <c r="AP24" s="43"/>
+      <c r="AQ24" s="43"/>
+      <c r="AR24" s="43"/>
+      <c r="AS24" s="43"/>
+      <c r="AT24" s="43"/>
+      <c r="AU24" s="43"/>
+      <c r="AV24" s="43"/>
+      <c r="AW24" s="43"/>
+      <c r="AX24" s="43"/>
+      <c r="AY24" s="43"/>
+      <c r="AZ24" s="43"/>
+      <c r="BA24" s="44"/>
     </row>
     <row r="25" spans="2:53">
-      <c r="B25" s="57"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="36"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="36"/>
-      <c r="O25" s="36"/>
-      <c r="P25" s="36"/>
-      <c r="Q25" s="36"/>
-      <c r="R25" s="36"/>
-      <c r="S25" s="36"/>
-      <c r="T25" s="36"/>
-      <c r="U25" s="36"/>
-      <c r="V25" s="36"/>
-      <c r="W25" s="36"/>
-      <c r="X25" s="36"/>
-      <c r="Y25" s="36"/>
-      <c r="Z25" s="36"/>
-      <c r="AA25" s="36"/>
-      <c r="AB25" s="36"/>
-      <c r="AC25" s="36"/>
-      <c r="AD25" s="36"/>
-      <c r="AE25" s="36"/>
-      <c r="AF25" s="36"/>
-      <c r="AG25" s="36"/>
-      <c r="AH25" s="36"/>
-      <c r="AI25" s="36"/>
-      <c r="AJ25" s="36"/>
-      <c r="AK25" s="36"/>
-      <c r="AL25" s="36"/>
-      <c r="AM25" s="36"/>
-      <c r="AN25" s="36"/>
-      <c r="AO25" s="36"/>
-      <c r="AP25" s="36"/>
-      <c r="AQ25" s="36"/>
-      <c r="AR25" s="36"/>
-      <c r="AS25" s="36"/>
-      <c r="AT25" s="36"/>
-      <c r="AU25" s="36"/>
-      <c r="AV25" s="36"/>
-      <c r="AW25" s="36"/>
-      <c r="AX25" s="36"/>
-      <c r="AY25" s="36"/>
-      <c r="AZ25" s="36"/>
-      <c r="BA25" s="58"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="43"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="43"/>
+      <c r="Q25" s="43"/>
+      <c r="R25" s="43"/>
+      <c r="S25" s="43"/>
+      <c r="T25" s="43"/>
+      <c r="U25" s="43"/>
+      <c r="V25" s="43"/>
+      <c r="W25" s="43"/>
+      <c r="X25" s="43"/>
+      <c r="Y25" s="43"/>
+      <c r="Z25" s="43"/>
+      <c r="AA25" s="43"/>
+      <c r="AB25" s="43"/>
+      <c r="AC25" s="43"/>
+      <c r="AD25" s="43"/>
+      <c r="AE25" s="43"/>
+      <c r="AF25" s="43"/>
+      <c r="AG25" s="43"/>
+      <c r="AH25" s="43"/>
+      <c r="AI25" s="43"/>
+      <c r="AJ25" s="43"/>
+      <c r="AK25" s="43"/>
+      <c r="AL25" s="43"/>
+      <c r="AM25" s="43"/>
+      <c r="AN25" s="43"/>
+      <c r="AO25" s="43"/>
+      <c r="AP25" s="43"/>
+      <c r="AQ25" s="43"/>
+      <c r="AR25" s="43"/>
+      <c r="AS25" s="43"/>
+      <c r="AT25" s="43"/>
+      <c r="AU25" s="43"/>
+      <c r="AV25" s="43"/>
+      <c r="AW25" s="43"/>
+      <c r="AX25" s="43"/>
+      <c r="AY25" s="43"/>
+      <c r="AZ25" s="43"/>
+      <c r="BA25" s="44"/>
     </row>
     <row r="26" spans="2:53">
-      <c r="B26" s="57"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="36"/>
-      <c r="K26" s="36"/>
-      <c r="L26" s="36"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="36"/>
-      <c r="O26" s="36"/>
-      <c r="P26" s="36"/>
-      <c r="Q26" s="36"/>
-      <c r="R26" s="36"/>
-      <c r="S26" s="36"/>
-      <c r="T26" s="36"/>
-      <c r="U26" s="36"/>
-      <c r="V26" s="36"/>
-      <c r="W26" s="36"/>
-      <c r="X26" s="36"/>
-      <c r="Y26" s="36"/>
-      <c r="Z26" s="36"/>
-      <c r="AA26" s="36"/>
-      <c r="AB26" s="36"/>
-      <c r="AC26" s="36"/>
-      <c r="AD26" s="36"/>
-      <c r="AE26" s="36"/>
-      <c r="AF26" s="36"/>
-      <c r="AG26" s="36"/>
-      <c r="AH26" s="36"/>
-      <c r="AI26" s="36"/>
-      <c r="AJ26" s="36"/>
-      <c r="AK26" s="36"/>
-      <c r="AL26" s="36"/>
-      <c r="AM26" s="36"/>
-      <c r="AN26" s="36"/>
-      <c r="AO26" s="36"/>
-      <c r="AP26" s="36"/>
-      <c r="AQ26" s="36"/>
-      <c r="AR26" s="36"/>
-      <c r="AS26" s="36"/>
-      <c r="AT26" s="36"/>
-      <c r="AU26" s="36"/>
-      <c r="AV26" s="36"/>
-      <c r="AW26" s="36"/>
-      <c r="AX26" s="36"/>
-      <c r="AY26" s="36"/>
-      <c r="AZ26" s="36"/>
-      <c r="BA26" s="58"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="X26" s="43"/>
+      <c r="Y26" s="43"/>
+      <c r="Z26" s="43"/>
+      <c r="AA26" s="43"/>
+      <c r="AB26" s="43"/>
+      <c r="AC26" s="43"/>
+      <c r="AD26" s="43"/>
+      <c r="AE26" s="43"/>
+      <c r="AF26" s="43"/>
+      <c r="AG26" s="43"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
+      <c r="AL26" s="43"/>
+      <c r="AM26" s="43"/>
+      <c r="AN26" s="43"/>
+      <c r="AO26" s="43"/>
+      <c r="AP26" s="43"/>
+      <c r="AQ26" s="43"/>
+      <c r="AR26" s="43"/>
+      <c r="AS26" s="43"/>
+      <c r="AT26" s="43"/>
+      <c r="AU26" s="43"/>
+      <c r="AV26" s="43"/>
+      <c r="AW26" s="43"/>
+      <c r="AX26" s="43"/>
+      <c r="AY26" s="43"/>
+      <c r="AZ26" s="43"/>
+      <c r="BA26" s="44"/>
     </row>
     <row r="27" spans="2:53">
-      <c r="B27" s="57"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="36"/>
-      <c r="K27" s="36"/>
-      <c r="L27" s="36"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="36"/>
-      <c r="O27" s="36"/>
-      <c r="P27" s="36"/>
-      <c r="Q27" s="36"/>
-      <c r="R27" s="36"/>
-      <c r="S27" s="36"/>
-      <c r="T27" s="36"/>
-      <c r="U27" s="36"/>
-      <c r="V27" s="36"/>
-      <c r="W27" s="36"/>
-      <c r="X27" s="36"/>
-      <c r="Y27" s="36"/>
-      <c r="Z27" s="36"/>
-      <c r="AA27" s="36"/>
-      <c r="AB27" s="36"/>
-      <c r="AC27" s="36"/>
-      <c r="AD27" s="36"/>
-      <c r="AE27" s="36"/>
-      <c r="AF27" s="36"/>
-      <c r="AG27" s="36"/>
-      <c r="AH27" s="36"/>
-      <c r="AI27" s="36"/>
-      <c r="AJ27" s="36"/>
-      <c r="AK27" s="36"/>
-      <c r="AL27" s="36"/>
-      <c r="AM27" s="36"/>
-      <c r="AN27" s="36"/>
-      <c r="AO27" s="36"/>
-      <c r="AP27" s="36"/>
-      <c r="AQ27" s="36"/>
-      <c r="AR27" s="36"/>
-      <c r="AS27" s="36"/>
-      <c r="AT27" s="36"/>
-      <c r="AU27" s="36"/>
-      <c r="AV27" s="36"/>
-      <c r="AW27" s="36"/>
-      <c r="AX27" s="36"/>
-      <c r="AY27" s="36"/>
-      <c r="AZ27" s="36"/>
-      <c r="BA27" s="58"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="43"/>
+      <c r="M27" s="43"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="43"/>
+      <c r="P27" s="43"/>
+      <c r="Q27" s="43"/>
+      <c r="R27" s="43"/>
+      <c r="S27" s="43"/>
+      <c r="T27" s="43"/>
+      <c r="U27" s="43"/>
+      <c r="V27" s="43"/>
+      <c r="W27" s="43"/>
+      <c r="X27" s="43"/>
+      <c r="Y27" s="43"/>
+      <c r="Z27" s="43"/>
+      <c r="AA27" s="43"/>
+      <c r="AB27" s="43"/>
+      <c r="AC27" s="43"/>
+      <c r="AD27" s="43"/>
+      <c r="AE27" s="43"/>
+      <c r="AF27" s="43"/>
+      <c r="AG27" s="43"/>
+      <c r="AH27" s="43"/>
+      <c r="AI27" s="43"/>
+      <c r="AJ27" s="43"/>
+      <c r="AK27" s="43"/>
+      <c r="AL27" s="43"/>
+      <c r="AM27" s="43"/>
+      <c r="AN27" s="43"/>
+      <c r="AO27" s="43"/>
+      <c r="AP27" s="43"/>
+      <c r="AQ27" s="43"/>
+      <c r="AR27" s="43"/>
+      <c r="AS27" s="43"/>
+      <c r="AT27" s="43"/>
+      <c r="AU27" s="43"/>
+      <c r="AV27" s="43"/>
+      <c r="AW27" s="43"/>
+      <c r="AX27" s="43"/>
+      <c r="AY27" s="43"/>
+      <c r="AZ27" s="43"/>
+      <c r="BA27" s="44"/>
     </row>
     <row r="28" spans="2:53">
-      <c r="B28" s="40"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="41"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="41"/>
-      <c r="O28" s="41"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="41"/>
-      <c r="S28" s="41"/>
-      <c r="T28" s="41"/>
-      <c r="U28" s="41"/>
-      <c r="V28" s="41"/>
-      <c r="W28" s="41"/>
-      <c r="X28" s="41"/>
-      <c r="Y28" s="41"/>
-      <c r="Z28" s="41"/>
-      <c r="AA28" s="41"/>
-      <c r="AB28" s="41"/>
-      <c r="AC28" s="41"/>
-      <c r="AD28" s="41"/>
-      <c r="AE28" s="41"/>
-      <c r="AF28" s="41"/>
-      <c r="AG28" s="41"/>
-      <c r="AH28" s="41"/>
-      <c r="AI28" s="41"/>
-      <c r="AJ28" s="41"/>
-      <c r="AK28" s="41"/>
-      <c r="AL28" s="41"/>
-      <c r="AM28" s="41"/>
-      <c r="AN28" s="41"/>
-      <c r="AO28" s="41"/>
-      <c r="AP28" s="41"/>
-      <c r="AQ28" s="41"/>
-      <c r="AR28" s="41"/>
-      <c r="AS28" s="41"/>
-      <c r="AT28" s="41"/>
-      <c r="AU28" s="41"/>
-      <c r="AV28" s="41"/>
-      <c r="AW28" s="41"/>
-      <c r="AX28" s="41"/>
-      <c r="AY28" s="41"/>
-      <c r="AZ28" s="41"/>
-      <c r="BA28" s="42"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="39"/>
+      <c r="N28" s="39"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="39"/>
+      <c r="Q28" s="39"/>
+      <c r="R28" s="39"/>
+      <c r="S28" s="39"/>
+      <c r="T28" s="39"/>
+      <c r="U28" s="39"/>
+      <c r="V28" s="39"/>
+      <c r="W28" s="39"/>
+      <c r="X28" s="39"/>
+      <c r="Y28" s="39"/>
+      <c r="Z28" s="39"/>
+      <c r="AA28" s="39"/>
+      <c r="AB28" s="39"/>
+      <c r="AC28" s="39"/>
+      <c r="AD28" s="39"/>
+      <c r="AE28" s="39"/>
+      <c r="AF28" s="39"/>
+      <c r="AG28" s="39"/>
+      <c r="AH28" s="39"/>
+      <c r="AI28" s="39"/>
+      <c r="AJ28" s="39"/>
+      <c r="AK28" s="39"/>
+      <c r="AL28" s="39"/>
+      <c r="AM28" s="39"/>
+      <c r="AN28" s="39"/>
+      <c r="AO28" s="39"/>
+      <c r="AP28" s="39"/>
+      <c r="AQ28" s="39"/>
+      <c r="AR28" s="39"/>
+      <c r="AS28" s="39"/>
+      <c r="AT28" s="39"/>
+      <c r="AU28" s="39"/>
+      <c r="AV28" s="39"/>
+      <c r="AW28" s="39"/>
+      <c r="AX28" s="39"/>
+      <c r="AY28" s="39"/>
+      <c r="AZ28" s="39"/>
+      <c r="BA28" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="27">
+    <mergeCell ref="A2:BD3"/>
+    <mergeCell ref="AH8:AM9"/>
+    <mergeCell ref="Q16:AA17"/>
+    <mergeCell ref="G8:AG9"/>
+    <mergeCell ref="AB16:AJ17"/>
+    <mergeCell ref="AQ17:BA17"/>
+    <mergeCell ref="AN6:BA7"/>
+    <mergeCell ref="AN12:BA13"/>
+    <mergeCell ref="B6:F7"/>
+    <mergeCell ref="G6:AG7"/>
+    <mergeCell ref="AH6:AM7"/>
     <mergeCell ref="AQ16:BA16"/>
     <mergeCell ref="AN8:BA9"/>
     <mergeCell ref="B23:BA28"/>
@@ -2627,21 +2693,9 @@
     <mergeCell ref="AH10:AM11"/>
     <mergeCell ref="AN10:BA11"/>
     <mergeCell ref="AI18:BA19"/>
-    <mergeCell ref="A2:BD3"/>
-    <mergeCell ref="B18:D19"/>
-    <mergeCell ref="AH8:AM9"/>
-    <mergeCell ref="Q16:AA17"/>
-    <mergeCell ref="G8:AG9"/>
-    <mergeCell ref="AB16:AJ17"/>
-    <mergeCell ref="AQ17:BA17"/>
-    <mergeCell ref="AN6:BA7"/>
-    <mergeCell ref="E16:P17"/>
-    <mergeCell ref="AN12:BA13"/>
-    <mergeCell ref="B6:F7"/>
-    <mergeCell ref="E18:P19"/>
-    <mergeCell ref="B16:D17"/>
-    <mergeCell ref="G6:AG7"/>
-    <mergeCell ref="AH6:AM7"/>
+    <mergeCell ref="B16:J17"/>
+    <mergeCell ref="K16:P17"/>
+    <mergeCell ref="B18:P19"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2669,7 +2723,7 @@
   <sheetData>
     <row r="1" spans="1:52" ht="14.25" customHeight="1">
       <c r="A1" s="33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:52" ht="14.25" customHeight="1">
@@ -3865,7 +3919,7 @@
   <sheetData>
     <row r="1" spans="1:55" ht="11.25" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -4924,62 +4978,62 @@
       <c r="AZ20" s="22"/>
     </row>
     <row r="21" spans="1:52" ht="11.25" customHeight="1" thickBot="1">
-      <c r="A21" s="68" t="s">
+      <c r="A21" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="73"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73"/>
+      <c r="J21" s="73"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="73"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="73"/>
+      <c r="O21" s="73"/>
+      <c r="P21" s="73"/>
+      <c r="Q21" s="73"/>
+      <c r="R21" s="73"/>
+      <c r="S21" s="73"/>
+      <c r="T21" s="73"/>
+      <c r="U21" s="73"/>
+      <c r="V21" s="73"/>
+      <c r="W21" s="73"/>
+      <c r="X21" s="73"/>
+      <c r="Y21" s="73"/>
+      <c r="Z21" s="79"/>
+      <c r="AA21" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="69"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="70"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="69"/>
-      <c r="J21" s="69"/>
-      <c r="K21" s="69"/>
-      <c r="L21" s="69"/>
-      <c r="M21" s="69"/>
-      <c r="N21" s="69"/>
-      <c r="O21" s="69"/>
-      <c r="P21" s="69"/>
-      <c r="Q21" s="69"/>
-      <c r="R21" s="69"/>
-      <c r="S21" s="69"/>
-      <c r="T21" s="69"/>
-      <c r="U21" s="69"/>
-      <c r="V21" s="69"/>
-      <c r="W21" s="69"/>
-      <c r="X21" s="69"/>
-      <c r="Y21" s="69"/>
-      <c r="Z21" s="75"/>
-      <c r="AA21" s="68" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB21" s="69"/>
-      <c r="AC21" s="69"/>
-      <c r="AD21" s="69"/>
-      <c r="AE21" s="69"/>
-      <c r="AF21" s="70"/>
-      <c r="AG21" s="74"/>
-      <c r="AH21" s="69"/>
-      <c r="AI21" s="69"/>
-      <c r="AJ21" s="69"/>
-      <c r="AK21" s="69"/>
-      <c r="AL21" s="69"/>
-      <c r="AM21" s="69"/>
-      <c r="AN21" s="69"/>
-      <c r="AO21" s="69"/>
-      <c r="AP21" s="69"/>
-      <c r="AQ21" s="69"/>
-      <c r="AR21" s="69"/>
-      <c r="AS21" s="69"/>
-      <c r="AT21" s="69"/>
-      <c r="AU21" s="69"/>
-      <c r="AV21" s="69"/>
-      <c r="AW21" s="69"/>
-      <c r="AX21" s="69"/>
-      <c r="AY21" s="69"/>
-      <c r="AZ21" s="75"/>
+      <c r="AB21" s="73"/>
+      <c r="AC21" s="73"/>
+      <c r="AD21" s="73"/>
+      <c r="AE21" s="73"/>
+      <c r="AF21" s="74"/>
+      <c r="AG21" s="78"/>
+      <c r="AH21" s="73"/>
+      <c r="AI21" s="73"/>
+      <c r="AJ21" s="73"/>
+      <c r="AK21" s="73"/>
+      <c r="AL21" s="73"/>
+      <c r="AM21" s="73"/>
+      <c r="AN21" s="73"/>
+      <c r="AO21" s="73"/>
+      <c r="AP21" s="73"/>
+      <c r="AQ21" s="73"/>
+      <c r="AR21" s="73"/>
+      <c r="AS21" s="73"/>
+      <c r="AT21" s="73"/>
+      <c r="AU21" s="73"/>
+      <c r="AV21" s="73"/>
+      <c r="AW21" s="73"/>
+      <c r="AX21" s="73"/>
+      <c r="AY21" s="73"/>
+      <c r="AZ21" s="79"/>
     </row>
     <row r="22" spans="1:52" ht="11.25" customHeight="1">
       <c r="A22" s="15"/>
@@ -6008,62 +6062,62 @@
       <c r="AZ40" s="22"/>
     </row>
     <row r="41" spans="1:52" ht="11.25" customHeight="1" thickBot="1">
-      <c r="A41" s="68" t="s">
+      <c r="A41" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" s="73"/>
+      <c r="C41" s="73"/>
+      <c r="D41" s="73"/>
+      <c r="E41" s="73"/>
+      <c r="F41" s="74"/>
+      <c r="G41" s="78"/>
+      <c r="H41" s="73"/>
+      <c r="I41" s="73"/>
+      <c r="J41" s="73"/>
+      <c r="K41" s="73"/>
+      <c r="L41" s="73"/>
+      <c r="M41" s="73"/>
+      <c r="N41" s="73"/>
+      <c r="O41" s="73"/>
+      <c r="P41" s="73"/>
+      <c r="Q41" s="73"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="73"/>
+      <c r="T41" s="73"/>
+      <c r="U41" s="73"/>
+      <c r="V41" s="73"/>
+      <c r="W41" s="73"/>
+      <c r="X41" s="73"/>
+      <c r="Y41" s="73"/>
+      <c r="Z41" s="79"/>
+      <c r="AA41" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="B41" s="69"/>
-      <c r="C41" s="69"/>
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="74"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="69"/>
-      <c r="L41" s="69"/>
-      <c r="M41" s="69"/>
-      <c r="N41" s="69"/>
-      <c r="O41" s="69"/>
-      <c r="P41" s="69"/>
-      <c r="Q41" s="69"/>
-      <c r="R41" s="69"/>
-      <c r="S41" s="69"/>
-      <c r="T41" s="69"/>
-      <c r="U41" s="69"/>
-      <c r="V41" s="69"/>
-      <c r="W41" s="69"/>
-      <c r="X41" s="69"/>
-      <c r="Y41" s="69"/>
-      <c r="Z41" s="75"/>
-      <c r="AA41" s="68" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB41" s="69"/>
-      <c r="AC41" s="69"/>
-      <c r="AD41" s="69"/>
-      <c r="AE41" s="69"/>
-      <c r="AF41" s="70"/>
-      <c r="AG41" s="74"/>
-      <c r="AH41" s="69"/>
-      <c r="AI41" s="69"/>
-      <c r="AJ41" s="69"/>
-      <c r="AK41" s="69"/>
-      <c r="AL41" s="69"/>
-      <c r="AM41" s="69"/>
-      <c r="AN41" s="69"/>
-      <c r="AO41" s="69"/>
-      <c r="AP41" s="69"/>
-      <c r="AQ41" s="69"/>
-      <c r="AR41" s="69"/>
-      <c r="AS41" s="69"/>
-      <c r="AT41" s="69"/>
-      <c r="AU41" s="69"/>
-      <c r="AV41" s="69"/>
-      <c r="AW41" s="69"/>
-      <c r="AX41" s="69"/>
-      <c r="AY41" s="69"/>
-      <c r="AZ41" s="75"/>
+      <c r="AB41" s="73"/>
+      <c r="AC41" s="73"/>
+      <c r="AD41" s="73"/>
+      <c r="AE41" s="73"/>
+      <c r="AF41" s="74"/>
+      <c r="AG41" s="78"/>
+      <c r="AH41" s="73"/>
+      <c r="AI41" s="73"/>
+      <c r="AJ41" s="73"/>
+      <c r="AK41" s="73"/>
+      <c r="AL41" s="73"/>
+      <c r="AM41" s="73"/>
+      <c r="AN41" s="73"/>
+      <c r="AO41" s="73"/>
+      <c r="AP41" s="73"/>
+      <c r="AQ41" s="73"/>
+      <c r="AR41" s="73"/>
+      <c r="AS41" s="73"/>
+      <c r="AT41" s="73"/>
+      <c r="AU41" s="73"/>
+      <c r="AV41" s="73"/>
+      <c r="AW41" s="73"/>
+      <c r="AX41" s="73"/>
+      <c r="AY41" s="73"/>
+      <c r="AZ41" s="79"/>
     </row>
     <row r="42" spans="1:52" ht="11.25" customHeight="1">
       <c r="A42" s="15"/>
@@ -7092,62 +7146,62 @@
       <c r="AZ60" s="22"/>
     </row>
     <row r="61" spans="1:52" ht="11.25" customHeight="1" thickBot="1">
-      <c r="A61" s="68" t="s">
-        <v>22</v>
+      <c r="A61" s="72" t="s">
+        <v>21</v>
       </c>
-      <c r="B61" s="69"/>
-      <c r="C61" s="69"/>
-      <c r="D61" s="69"/>
-      <c r="E61" s="69"/>
-      <c r="F61" s="70"/>
-      <c r="G61" s="71"/>
-      <c r="H61" s="72"/>
-      <c r="I61" s="72"/>
-      <c r="J61" s="72"/>
-      <c r="K61" s="72"/>
-      <c r="L61" s="72"/>
-      <c r="M61" s="72"/>
-      <c r="N61" s="72"/>
-      <c r="O61" s="72"/>
-      <c r="P61" s="72"/>
-      <c r="Q61" s="72"/>
-      <c r="R61" s="72"/>
-      <c r="S61" s="72"/>
-      <c r="T61" s="72"/>
-      <c r="U61" s="72"/>
-      <c r="V61" s="72"/>
-      <c r="W61" s="72"/>
-      <c r="X61" s="72"/>
-      <c r="Y61" s="72"/>
-      <c r="Z61" s="73"/>
-      <c r="AA61" s="68" t="s">
-        <v>25</v>
+      <c r="B61" s="73"/>
+      <c r="C61" s="73"/>
+      <c r="D61" s="73"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="74"/>
+      <c r="G61" s="75"/>
+      <c r="H61" s="76"/>
+      <c r="I61" s="76"/>
+      <c r="J61" s="76"/>
+      <c r="K61" s="76"/>
+      <c r="L61" s="76"/>
+      <c r="M61" s="76"/>
+      <c r="N61" s="76"/>
+      <c r="O61" s="76"/>
+      <c r="P61" s="76"/>
+      <c r="Q61" s="76"/>
+      <c r="R61" s="76"/>
+      <c r="S61" s="76"/>
+      <c r="T61" s="76"/>
+      <c r="U61" s="76"/>
+      <c r="V61" s="76"/>
+      <c r="W61" s="76"/>
+      <c r="X61" s="76"/>
+      <c r="Y61" s="76"/>
+      <c r="Z61" s="77"/>
+      <c r="AA61" s="72" t="s">
+        <v>24</v>
       </c>
-      <c r="AB61" s="69"/>
-      <c r="AC61" s="69"/>
-      <c r="AD61" s="69"/>
-      <c r="AE61" s="69"/>
-      <c r="AF61" s="70"/>
-      <c r="AG61" s="71"/>
-      <c r="AH61" s="72"/>
-      <c r="AI61" s="72"/>
-      <c r="AJ61" s="72"/>
-      <c r="AK61" s="72"/>
-      <c r="AL61" s="72"/>
-      <c r="AM61" s="72"/>
-      <c r="AN61" s="72"/>
-      <c r="AO61" s="72"/>
-      <c r="AP61" s="72"/>
-      <c r="AQ61" s="72"/>
-      <c r="AR61" s="72"/>
-      <c r="AS61" s="72"/>
-      <c r="AT61" s="72"/>
-      <c r="AU61" s="72"/>
-      <c r="AV61" s="72"/>
-      <c r="AW61" s="72"/>
-      <c r="AX61" s="72"/>
-      <c r="AY61" s="72"/>
-      <c r="AZ61" s="73"/>
+      <c r="AB61" s="73"/>
+      <c r="AC61" s="73"/>
+      <c r="AD61" s="73"/>
+      <c r="AE61" s="73"/>
+      <c r="AF61" s="74"/>
+      <c r="AG61" s="75"/>
+      <c r="AH61" s="76"/>
+      <c r="AI61" s="76"/>
+      <c r="AJ61" s="76"/>
+      <c r="AK61" s="76"/>
+      <c r="AL61" s="76"/>
+      <c r="AM61" s="76"/>
+      <c r="AN61" s="76"/>
+      <c r="AO61" s="76"/>
+      <c r="AP61" s="76"/>
+      <c r="AQ61" s="76"/>
+      <c r="AR61" s="76"/>
+      <c r="AS61" s="76"/>
+      <c r="AT61" s="76"/>
+      <c r="AU61" s="76"/>
+      <c r="AV61" s="76"/>
+      <c r="AW61" s="76"/>
+      <c r="AX61" s="76"/>
+      <c r="AY61" s="76"/>
+      <c r="AZ61" s="77"/>
     </row>
     <row r="62" spans="1:52">
       <c r="A62" s="15"/>
@@ -7960,65 +8014,73 @@
       <c r="AZ76" s="22"/>
     </row>
     <row r="77" spans="1:52" ht="14.25" thickBot="1">
-      <c r="A77" s="68" t="s">
+      <c r="A77" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="B77" s="73"/>
+      <c r="C77" s="73"/>
+      <c r="D77" s="73"/>
+      <c r="E77" s="73"/>
+      <c r="F77" s="74"/>
+      <c r="G77" s="75"/>
+      <c r="H77" s="76"/>
+      <c r="I77" s="76"/>
+      <c r="J77" s="76"/>
+      <c r="K77" s="76"/>
+      <c r="L77" s="76"/>
+      <c r="M77" s="76"/>
+      <c r="N77" s="76"/>
+      <c r="O77" s="76"/>
+      <c r="P77" s="76"/>
+      <c r="Q77" s="76"/>
+      <c r="R77" s="76"/>
+      <c r="S77" s="76"/>
+      <c r="T77" s="76"/>
+      <c r="U77" s="76"/>
+      <c r="V77" s="76"/>
+      <c r="W77" s="76"/>
+      <c r="X77" s="76"/>
+      <c r="Y77" s="76"/>
+      <c r="Z77" s="77"/>
+      <c r="AA77" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="B77" s="69"/>
-      <c r="C77" s="69"/>
-      <c r="D77" s="69"/>
-      <c r="E77" s="69"/>
-      <c r="F77" s="70"/>
-      <c r="G77" s="71"/>
-      <c r="H77" s="72"/>
-      <c r="I77" s="72"/>
-      <c r="J77" s="72"/>
-      <c r="K77" s="72"/>
-      <c r="L77" s="72"/>
-      <c r="M77" s="72"/>
-      <c r="N77" s="72"/>
-      <c r="O77" s="72"/>
-      <c r="P77" s="72"/>
-      <c r="Q77" s="72"/>
-      <c r="R77" s="72"/>
-      <c r="S77" s="72"/>
-      <c r="T77" s="72"/>
-      <c r="U77" s="72"/>
-      <c r="V77" s="72"/>
-      <c r="W77" s="72"/>
-      <c r="X77" s="72"/>
-      <c r="Y77" s="72"/>
-      <c r="Z77" s="73"/>
-      <c r="AA77" s="68" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB77" s="69"/>
-      <c r="AC77" s="69"/>
-      <c r="AD77" s="69"/>
-      <c r="AE77" s="69"/>
-      <c r="AF77" s="70"/>
-      <c r="AG77" s="71"/>
-      <c r="AH77" s="72"/>
-      <c r="AI77" s="72"/>
-      <c r="AJ77" s="72"/>
-      <c r="AK77" s="72"/>
-      <c r="AL77" s="72"/>
-      <c r="AM77" s="72"/>
-      <c r="AN77" s="72"/>
-      <c r="AO77" s="72"/>
-      <c r="AP77" s="72"/>
-      <c r="AQ77" s="72"/>
-      <c r="AR77" s="72"/>
-      <c r="AS77" s="72"/>
-      <c r="AT77" s="72"/>
-      <c r="AU77" s="72"/>
-      <c r="AV77" s="72"/>
-      <c r="AW77" s="72"/>
-      <c r="AX77" s="72"/>
-      <c r="AY77" s="72"/>
-      <c r="AZ77" s="73"/>
+      <c r="AB77" s="73"/>
+      <c r="AC77" s="73"/>
+      <c r="AD77" s="73"/>
+      <c r="AE77" s="73"/>
+      <c r="AF77" s="74"/>
+      <c r="AG77" s="75"/>
+      <c r="AH77" s="76"/>
+      <c r="AI77" s="76"/>
+      <c r="AJ77" s="76"/>
+      <c r="AK77" s="76"/>
+      <c r="AL77" s="76"/>
+      <c r="AM77" s="76"/>
+      <c r="AN77" s="76"/>
+      <c r="AO77" s="76"/>
+      <c r="AP77" s="76"/>
+      <c r="AQ77" s="76"/>
+      <c r="AR77" s="76"/>
+      <c r="AS77" s="76"/>
+      <c r="AT77" s="76"/>
+      <c r="AU77" s="76"/>
+      <c r="AV77" s="76"/>
+      <c r="AW77" s="76"/>
+      <c r="AX77" s="76"/>
+      <c r="AY77" s="76"/>
+      <c r="AZ77" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="G21:Z21"/>
+    <mergeCell ref="AA21:AF21"/>
+    <mergeCell ref="AG21:AZ21"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="G41:Z41"/>
+    <mergeCell ref="AA41:AF41"/>
+    <mergeCell ref="AG41:AZ41"/>
     <mergeCell ref="A77:F77"/>
     <mergeCell ref="G77:Z77"/>
     <mergeCell ref="AA77:AF77"/>
@@ -8027,14 +8089,6 @@
     <mergeCell ref="G61:Z61"/>
     <mergeCell ref="AA61:AF61"/>
     <mergeCell ref="AG61:AZ61"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="G21:Z21"/>
-    <mergeCell ref="AA21:AF21"/>
-    <mergeCell ref="AG21:AZ21"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="G41:Z41"/>
-    <mergeCell ref="AA41:AF41"/>
-    <mergeCell ref="AG41:AZ41"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="1">
